--- a/cs/Mazpen4AlefPresence.xlsx
+++ b/cs/Mazpen4AlefPresence.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\stra\repos\BeautifulYesodot\cs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0481B0E1-6C01-4B4B-B252-08E0B899C26A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D1DCCA-398B-4F9E-B1DA-32342D40134F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="3075" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="data" sheetId="1" r:id="rId1"/>
+    <sheet name="חלק א" sheetId="1" r:id="rId1"/>
+    <sheet name="חלק ב" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="95">
   <si>
     <t>שם</t>
   </si>
@@ -224,13 +225,94 @@
   </si>
   <si>
     <t>רשימה סגורה. סה"כ 12 נרשמים</t>
+  </si>
+  <si>
+    <t>יום ג׳ 12/5</t>
+  </si>
+  <si>
+    <t>יום א׳ 17/5</t>
+  </si>
+  <si>
+    <t>יום ג׳ 19/5</t>
+  </si>
+  <si>
+    <t>יום ב׳ 25/5</t>
+  </si>
+  <si>
+    <t>יום ד׳ 27/5</t>
+  </si>
+  <si>
+    <t>יום ב׳ 1/6</t>
+  </si>
+  <si>
+    <t>יום ד׳ 3/6</t>
+  </si>
+  <si>
+    <t>יום א׳ 7/6</t>
+  </si>
+  <si>
+    <t>יום ג׳ 9/6</t>
+  </si>
+  <si>
+    <t>יום ד׳ 24/6</t>
+  </si>
+  <si>
+    <t>יום א׳ 28/6</t>
+  </si>
+  <si>
+    <t>יום א׳ 5/7</t>
+  </si>
+  <si>
+    <t>יום ה׳ 9/7</t>
+  </si>
+  <si>
+    <t>יום ב׳ 13/7</t>
+  </si>
+  <si>
+    <t>יום ה׳ 16/7</t>
+  </si>
+  <si>
+    <t>יום א׳ 19/7</t>
+  </si>
+  <si>
+    <t>יום ג׳ 21/7</t>
+  </si>
+  <si>
+    <t>יום ו׳ 24/7</t>
+  </si>
+  <si>
+    <t>יום א׳ 26/7</t>
+  </si>
+  <si>
+    <t>בעייה עם התיק הוראה שהוא טיפל בה בעמל רב</t>
+  </si>
+  <si>
+    <t>עידו אדרי</t>
+  </si>
+  <si>
+    <t>משה יעקב אוריאל</t>
+  </si>
+  <si>
+    <t>052-6209276</t>
+  </si>
+  <si>
+    <t>מרכז פסג"ה באר שבע</t>
+  </si>
+  <si>
+    <t>מקיף ע"ש יצחק רבין</t>
+  </si>
+  <si>
+    <t>ציון מטלה מסכמת</t>
+  </si>
+  <si>
+    <t>לא מתחום הדעת בשפת c#</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,16 +328,34 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Assistant"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -263,11 +363,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -277,6 +392,20 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -616,15 +745,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.625" customWidth="1"/>
-    <col min="2" max="3" width="13.75" style="1" hidden="1" customWidth="1"/>
-    <col min="4" max="6" width="0" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="25.25" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="6.625" style="1" hidden="1" customWidth="1"/>
-    <col min="9" max="20" width="0" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="13.75" style="1" customWidth="1"/>
+    <col min="4" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="25.25" customWidth="1"/>
+    <col min="8" max="8" width="6.625" style="1" customWidth="1"/>
+    <col min="9" max="20" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
@@ -646,6 +775,12 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B3" s="2"/>
@@ -657,7 +792,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -683,12 +818,45 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="U5" s="4">
+    <row r="5" spans="1:22" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I5" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="R5" s="4">
         <v>46188</v>
       </c>
-      <c r="V5" s="4">
+      <c r="S5" s="4">
+        <v>46191</v>
+      </c>
+      <c r="T5" s="4">
         <v>46194</v>
+      </c>
+      <c r="V5" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
@@ -778,11 +946,8 @@
       <c r="T7">
         <v>1</v>
       </c>
-      <c r="U7">
-        <v>1</v>
-      </c>
       <c r="V7">
-        <v>1</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
@@ -846,11 +1011,8 @@
       <c r="T8">
         <v>1</v>
       </c>
-      <c r="U8">
-        <v>1</v>
-      </c>
-      <c r="V8">
-        <v>1</v>
+      <c r="V8" s="8">
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
@@ -914,11 +1076,8 @@
       <c r="T9">
         <v>1</v>
       </c>
-      <c r="U9">
-        <v>1</v>
-      </c>
-      <c r="V9">
-        <v>1</v>
+      <c r="V9" s="8">
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
@@ -982,11 +1141,8 @@
       <c r="T10">
         <v>1</v>
       </c>
-      <c r="U10">
-        <v>1</v>
-      </c>
-      <c r="V10">
-        <v>1</v>
+      <c r="V10" s="8">
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
@@ -1050,11 +1206,8 @@
       <c r="T11">
         <v>1</v>
       </c>
-      <c r="U11">
-        <v>1</v>
-      </c>
-      <c r="V11">
-        <v>1</v>
+      <c r="V11" s="8">
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
@@ -1082,6 +1235,10 @@
       <c r="H12" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="V12" s="8"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -1144,11 +1301,8 @@
       <c r="T13">
         <v>1</v>
       </c>
-      <c r="U13">
-        <v>1</v>
-      </c>
-      <c r="V13">
-        <v>1</v>
+      <c r="V13" s="8">
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
@@ -1212,11 +1366,8 @@
       <c r="T14">
         <v>1</v>
       </c>
-      <c r="U14">
-        <v>1</v>
-      </c>
-      <c r="V14">
-        <v>1</v>
+      <c r="V14" s="8">
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
@@ -1244,6 +1395,10 @@
       <c r="H15" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="V15" s="8"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -1306,14 +1461,11 @@
       <c r="T16">
         <v>1</v>
       </c>
-      <c r="U16">
-        <v>1</v>
-      </c>
-      <c r="V16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="V16" s="8">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>61</v>
       </c>
@@ -1343,6 +1495,54 @@
       </c>
       <c r="J17">
         <v>1</v>
+      </c>
+      <c r="V17" s="8"/>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>88</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>1</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="V18" s="8">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1352,4 +1552,525 @@
     <ignoredError sqref="A6:H17 A4:H4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DEB1B47-DEEC-43DD-90F5-A3E243622F73}">
+  <dimension ref="A1:T13"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="3" width="13.75" style="1" customWidth="1"/>
+    <col min="4" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="25.25" customWidth="1"/>
+    <col min="8" max="8" width="6.625" style="1" customWidth="1"/>
+    <col min="9" max="17" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B1" s="2">
+        <v>216180</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I5" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q5" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="R5" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1">
+        <v>34473751</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>416792</v>
+      </c>
+      <c r="E7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1">
+        <v>300566726</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8">
+        <v>516823</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="1">
+        <v>24934069</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9">
+        <v>456053</v>
+      </c>
+      <c r="E9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="1">
+        <v>57147902</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10">
+        <v>416800</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="1">
+        <v>314107822</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11">
+        <v>616847</v>
+      </c>
+      <c r="E11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="1">
+        <v>11763539</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12">
+        <v>416792</v>
+      </c>
+      <c r="E12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="T12">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="9">
+        <v>29004488</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" s="9">
+        <v>616821</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8">
+        <v>1</v>
+      </c>
+      <c r="K13" s="8">
+        <v>1</v>
+      </c>
+      <c r="L13" s="8">
+        <v>1</v>
+      </c>
+      <c r="M13" s="8">
+        <v>1</v>
+      </c>
+      <c r="N13" s="8">
+        <v>1</v>
+      </c>
+      <c r="O13" s="8">
+        <v>1</v>
+      </c>
+      <c r="P13" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>1</v>
+      </c>
+      <c r="R13" s="8">
+        <v>1</v>
+      </c>
+      <c r="T13">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>